--- a/output/xlsx/CombinandoExtracoesDiferentesPerfis--GT-.xlsx
+++ b/output/xlsx/CombinandoExtracoesDiferentesPerfis--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Precondition: </t>
   </si>
   <si>
-    <t>Administrador deve estar logado ; não existem extrações cadastradas</t>
+    <t>Usuário deve estar logado no servidor e extrator como administrador ; Deve existir um usuário cadastrado com perfil de operador</t>
   </si>
   <si>
     <t>#</t>
@@ -92,7 +92,7 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>administrador: pressiona opção “Extract from directory”</t>
+    <t>administrador: pressiona opção “Extract from dicrtory”</t>
   </si>
   <si>
     <t/>
@@ -119,52 +119,16 @@
     <t>SYSTEM exibe página de login</t>
   </si>
   <si>
-    <t>operator: faz login e vai para a página “Extractions”</t>
+    <t>administrador: faz login como operador e vai para a página “Extractions”</t>
   </si>
   <si>
     <t>SYSTEM exibe uma lista vazia</t>
   </si>
   <si>
-    <t>operator: pressiona opção “Extract from directory”</t>
-  </si>
-  <si>
-    <t>operator: seleciona pasta “Ext1”, que contém um único conjunto de arquivos para a família “IPP320-01T1220A”, e pressiona o botão “Extract”</t>
-  </si>
-  <si>
-    <t>operator: acessa página “Extractions”</t>
-  </si>
-  <si>
-    <t>operator: faz logout</t>
-  </si>
-  <si>
-    <t>operatorDois: faz login e vai para a página “Extractions”</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe uma lista com uma extração</t>
-  </si>
-  <si>
-    <t>operatorDois: faz logout</t>
-  </si>
-  <si>
-    <t>manager: faz login e vai para a página “Extractions”</t>
-  </si>
-  <si>
-    <t>manager: pressiona opção “Extract from directory”</t>
-  </si>
-  <si>
-    <t>manager: seleciona pasta “Ext1”, que contém um único conjunto de arquivos para a família “IPP320-01T1220A”, e pressiona o botão “Extract”</t>
-  </si>
-  <si>
-    <t>manager: acessa página “Extractions”</t>
-  </si>
-  <si>
-    <t>manager: faz logout</t>
-  </si>
-  <si>
-    <t>superAdministrador: faz login e vai para a página “Extractions”</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe lista com três extrações</t>
+    <t>administrador: faz login como administrador e vai para a página “Extractions”</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe uma lista com duas entradas</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -259,7 +223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -467,7 +431,7 @@
         <v>6.0</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s" s="3">
         <v>27</v>
@@ -487,7 +451,7 @@
         <v>7.0</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s" s="3">
         <v>27</v>
@@ -507,7 +471,7 @@
         <v>8.0</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s" s="3">
         <v>27</v>
@@ -527,7 +491,7 @@
         <v>9.0</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s" s="3">
         <v>27</v>
@@ -547,13 +511,13 @@
         <v>10.0</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D19" t="s" s="3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s" s="3">
         <v>27</v>
@@ -563,150 +527,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n" s="4">
-        <v>11.0</v>
-      </c>
-      <c r="B20" t="s" s="3">
-        <v>43</v>
-      </c>
-      <c r="C20" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D20" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E20" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F20" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n" s="4">
-        <v>12.0</v>
-      </c>
-      <c r="B21" t="s" s="3">
-        <v>44</v>
-      </c>
-      <c r="C21" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D21" t="s" s="3">
-        <v>36</v>
-      </c>
-      <c r="E21" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F21" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n" s="4">
-        <v>13.0</v>
-      </c>
-      <c r="B22" t="s" s="3">
-        <v>45</v>
-      </c>
-      <c r="C22" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D22" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E22" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F22" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n" s="4">
-        <v>14.0</v>
-      </c>
-      <c r="B23" t="s" s="3">
-        <v>46</v>
-      </c>
-      <c r="C23" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D23" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E23" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F23" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n" s="4">
-        <v>15.0</v>
-      </c>
-      <c r="B24" t="s" s="3">
-        <v>47</v>
-      </c>
-      <c r="C24" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D24" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E24" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F24" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n" s="4">
-        <v>16.0</v>
-      </c>
-      <c r="B25" t="s" s="3">
-        <v>48</v>
-      </c>
-      <c r="C25" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D25" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E25" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F25" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n" s="4">
-        <v>17.0</v>
-      </c>
-      <c r="B26" t="s" s="3">
-        <v>49</v>
-      </c>
-      <c r="C26" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D26" t="s" s="3">
-        <v>50</v>
-      </c>
-      <c r="E26" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F26" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B27" t="s" s="0">
+      <c r="A20" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s" s="0">
         <v>27</v>
       </c>
     </row>
